--- a/docs/oc-regiones/seguro-colectivo-de-vida-con-adicional-de-salud/lib-gral-bdo-o-higgins.xlsx
+++ b/docs/oc-regiones/seguro-colectivo-de-vida-con-adicional-de-salud/lib-gral-bdo-o-higgins.xlsx
@@ -569,7 +569,7 @@
         </is>
       </c>
       <c r="M2" s="2" t="n">
-        <v>73379.10000000001</v>
+        <v>71502.32000000001</v>
       </c>
     </row>
     <row r="3">
@@ -630,7 +630,7 @@
         </is>
       </c>
       <c r="M3" s="2" t="n">
-        <v>51483.72</v>
+        <v>51153.93</v>
       </c>
     </row>
     <row r="4">
@@ -691,7 +691,7 @@
         </is>
       </c>
       <c r="M4" s="2" t="n">
-        <v>22292.41</v>
+        <v>22149.61</v>
       </c>
     </row>
   </sheetData>

--- a/docs/oc-regiones/seguro-colectivo-de-vida-con-adicional-de-salud/lib-gral-bdo-o-higgins.xlsx
+++ b/docs/oc-regiones/seguro-colectivo-de-vida-con-adicional-de-salud/lib-gral-bdo-o-higgins.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M4"/>
+  <dimension ref="A1:M6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -514,7 +514,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>1076575-1-CM26</t>
+          <t>1076575-1-CM25</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -524,12 +524,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>ene-2026</t>
+          <t>feb-2025</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2026-01-02</t>
+          <t>2025-02-19</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -569,13 +569,13 @@
         </is>
       </c>
       <c r="M2" s="2" t="n">
-        <v>71502.32000000001</v>
+        <v>52696.62</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>544515-1-CM26</t>
+          <t>1076575-2-CM25</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -585,12 +585,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>ene-2026</t>
+          <t>feb-2025</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2026-01-21</t>
+          <t>2025-02-28</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -600,12 +600,12 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>72.240.400-9</t>
+          <t>60.110.000-2</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>GOBIERNO REGIONAL VI REGION DEL LI BERTADOR B O"HIGGINS</t>
+          <t>INSTITUTO NACIONAL DE LA JUVENTUD</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -630,13 +630,13 @@
         </is>
       </c>
       <c r="M3" s="2" t="n">
-        <v>51153.93</v>
+        <v>22882.98</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>544515-2-CM26</t>
+          <t>1076575-1-CM26</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -651,7 +651,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2026-01-21</t>
+          <t>2026-01-02</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -661,12 +661,12 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>72.240.400-9</t>
+          <t>60.110.000-2</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>GOBIERNO REGIONAL VI REGION DEL LI BERTADOR B O"HIGGINS</t>
+          <t>INSTITUTO NACIONAL DE LA JUVENTUD</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -691,6 +691,128 @@
         </is>
       </c>
       <c r="M4" s="2" t="n">
+        <v>71502.32000000001</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>544515-1-CM26</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>2239-12-LR23</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>ene-2026</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>2026-01-21</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>72.240.400-9</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>GOBIERNO REGIONAL VI REGION DEL LI BERTADOR B O"HIGGINS</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Lib. Gral. Bdo. O'Higgins</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>BCI SEGUROS VIDA S A</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>96.573.600-K</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="n">
+        <v>51153.93</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>544515-2-CM26</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>2239-12-LR23</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>ene-2026</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>2026-01-21</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>72.240.400-9</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>GOBIERNO REGIONAL VI REGION DEL LI BERTADOR B O"HIGGINS</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Lib. Gral. Bdo. O'Higgins</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>BCI SEGUROS VIDA S A</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>96.573.600-K</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="n">
         <v>22149.61</v>
       </c>
     </row>
